--- a/02_Inputs/Data/Charts/Module 3 - Dasasets for Charts.xlsx
+++ b/02_Inputs/Data/Charts/Module 3 - Dasasets for Charts.xlsx
@@ -1,17 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29012"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="648" documentId="11_86B3BED064903DA954D0E649743742B46DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E00FE5DF-CB7F-4EB7-93C8-D9BDCD0B71BC}"/>
+  <xr:revisionPtr revIDLastSave="714" documentId="11_86B3BED064903DA954D0E649743742B46DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0942F98D-A3CC-456D-9EF2-8CA29F61922A}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M3_C2_7" sheetId="1" r:id="rId1"/>
-    <sheet name="M3_C3_11" sheetId="2" r:id="rId2"/>
-    <sheet name="M3_C2_12" sheetId="3" r:id="rId3"/>
-    <sheet name="M3_C3_15" sheetId="4" r:id="rId4"/>
+    <sheet name="M3_C3_11_1" sheetId="2" r:id="rId2"/>
+    <sheet name="M3_C3_11_2" sheetId="5" r:id="rId3"/>
+    <sheet name="M3_C3_12_1" sheetId="3" r:id="rId4"/>
+    <sheet name="M3_C3_12_2" sheetId="7" r:id="rId5"/>
+    <sheet name="M3_C3_12_3" sheetId="8" r:id="rId6"/>
+    <sheet name="M3_C3_12_4" sheetId="9" r:id="rId7"/>
+    <sheet name="M3_C3_15" sheetId="4" r:id="rId8"/>
+    <sheet name="(Legacy) M3_C3_11" sheetId="6" r:id="rId9"/>
+    <sheet name="(Legacy) M3_C2_12" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -34,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="79">
   <si>
     <t>Sector</t>
   </si>
@@ -144,12 +150,117 @@
     <t>Natural gas</t>
   </si>
   <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Clean energy</t>
+  </si>
+  <si>
+    <t>Other uses</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Hard coal</t>
+  </si>
+  <si>
+    <t>PC, without CCS</t>
+  </si>
+  <si>
+    <t>IGCC, without CCS</t>
+  </si>
+  <si>
+    <t>SC, without CCS</t>
+  </si>
+  <si>
+    <t>NGCC, without CCS</t>
+  </si>
+  <si>
+    <t>PC, with CCS</t>
+  </si>
+  <si>
+    <t>IGCC, with CCS</t>
+  </si>
+  <si>
+    <t>SC, with CCS</t>
+  </si>
+  <si>
+    <t>NGCC, with CCS</t>
+  </si>
+  <si>
+    <t>Hydro</t>
+  </si>
+  <si>
+    <t>660 MW</t>
+  </si>
+  <si>
+    <t>360 MW</t>
+  </si>
+  <si>
+    <t>Nuclear</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>CSP</t>
+  </si>
+  <si>
+    <t>tower</t>
+  </si>
+  <si>
+    <t>trough</t>
+  </si>
+  <si>
+    <t>PV</t>
+  </si>
+  <si>
+    <t>poly-Si, ground-mounted</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> poly-Si, roof-mounted</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CdTe, ground-mounted</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CdTe, roof-mounted</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CIGS, ground-mounted</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CIGS, roof-mounted</t>
+  </si>
+  <si>
+    <t>Wind</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> onshore</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> offshore, concrete foundation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> offshore, steel foundation</t>
+  </si>
+  <si>
     <t>Mineral</t>
   </si>
   <si>
-    <t>Year</t>
-  </si>
-  <si>
     <t>Clean energy kt</t>
   </si>
   <si>
@@ -166,105 +277,6 @@
   </si>
   <si>
     <t>Neodymium</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Hard coal</t>
-  </si>
-  <si>
-    <t>PC, without CCS</t>
-  </si>
-  <si>
-    <t>IGCC, without CCS</t>
-  </si>
-  <si>
-    <t>SC, without CCS</t>
-  </si>
-  <si>
-    <t>NGCC, without CCS</t>
-  </si>
-  <si>
-    <t>PC, with CCS</t>
-  </si>
-  <si>
-    <t>IGCC, with CCS</t>
-  </si>
-  <si>
-    <t>SC, with CCS</t>
-  </si>
-  <si>
-    <t>NGCC, with CCS</t>
-  </si>
-  <si>
-    <t>Hydro</t>
-  </si>
-  <si>
-    <t>660 MW</t>
-  </si>
-  <si>
-    <t>360 MW</t>
-  </si>
-  <si>
-    <t>Nuclear</t>
-  </si>
-  <si>
-    <t>average</t>
-  </si>
-  <si>
-    <t>CSP</t>
-  </si>
-  <si>
-    <t>tower</t>
-  </si>
-  <si>
-    <t>trough</t>
-  </si>
-  <si>
-    <t>PV</t>
-  </si>
-  <si>
-    <t>poly-Si, ground-mounted</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> poly-Si, roof-mounted</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CdTe, ground-mounted</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CdTe, roof-mounted</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CIGS, ground-mounted</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CIGS, roof-mounted</t>
-  </si>
-  <si>
-    <t>Wind</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> onshore</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> offshore, concrete foundation</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> offshore, steel foundation</t>
   </si>
 </sst>
 </file>
@@ -425,7 +437,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -512,6 +524,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -851,6 +864,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1072,8 +1088,1228 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3416D971-AC8D-4ECA-A9B5-B8058DC8EE89}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="19">
+        <v>2017</v>
+      </c>
+      <c r="C2" s="19">
+        <v>12.833099579242599</v>
+      </c>
+      <c r="D2" s="19">
+        <v>30</v>
+      </c>
+      <c r="E2" s="19">
+        <v>43.758765778401099</v>
+      </c>
+      <c r="F2" s="19">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="19">
+        <v>2022</v>
+      </c>
+      <c r="C3" s="19">
+        <v>73.211781206171096</v>
+      </c>
+      <c r="D3" s="19">
+        <v>56</v>
+      </c>
+      <c r="E3" s="19">
+        <v>130.434782608695</v>
+      </c>
+      <c r="F3" s="19">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="20">
+        <v>2017</v>
+      </c>
+      <c r="C4" s="16">
+        <v>127.490039840637</v>
+      </c>
+      <c r="D4" s="16">
+        <v>6</v>
+      </c>
+      <c r="E4" s="16">
+        <v>2175.2988047808699</v>
+      </c>
+      <c r="F4" s="16">
+        <f>100-D4</f>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="20">
+        <v>2022</v>
+      </c>
+      <c r="C5" s="16">
+        <v>456.765530470709</v>
+      </c>
+      <c r="D5" s="16">
+        <v>16</v>
+      </c>
+      <c r="E5" s="16">
+        <v>2932.9718164379501</v>
+      </c>
+      <c r="F5" s="16">
+        <f>100-D5</f>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="19">
+        <v>2017</v>
+      </c>
+      <c r="C6" s="15">
+        <v>16.399286987522199</v>
+      </c>
+      <c r="D6" s="15">
+        <v>17</v>
+      </c>
+      <c r="E6" s="15">
+        <v>99.108734402851994</v>
+      </c>
+      <c r="F6" s="15">
+        <f t="shared" ref="F6:F9" si="0">100-D6</f>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="19">
+        <v>2022</v>
+      </c>
+      <c r="C7" s="15">
+        <v>68.449197860962499</v>
+      </c>
+      <c r="D7" s="15">
+        <v>40</v>
+      </c>
+      <c r="E7" s="15">
+        <v>171.12299465240599</v>
+      </c>
+      <c r="F7" s="15">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="20">
+        <v>2017</v>
+      </c>
+      <c r="C8" s="16">
+        <v>2.77456275720162</v>
+      </c>
+      <c r="D8" s="16">
+        <v>7</v>
+      </c>
+      <c r="E8" s="16">
+        <v>42.2590342078189</v>
+      </c>
+      <c r="F8" s="16">
+        <f t="shared" si="0"/>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="20">
+        <v>2022</v>
+      </c>
+      <c r="C9" s="16">
+        <v>9.6064814814814596</v>
+      </c>
+      <c r="D9" s="16">
+        <v>10</v>
+      </c>
+      <c r="E9" s="16">
+        <v>96.5125064300411</v>
+      </c>
+      <c r="F9" s="16">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7FED632-61F3-4BCA-B00D-790FFD606C75}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A1" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="15">
+        <v>66.297208538587796</v>
+      </c>
+      <c r="D2" s="15">
+        <v>53.160919540229202</v>
+      </c>
+      <c r="E2" s="15">
+        <v>13.067870826491003</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0</v>
+      </c>
+      <c r="G2" s="15">
+        <v>39.340448823207993</v>
+      </c>
+      <c r="H2" s="6">
+        <v>0</v>
+      </c>
+      <c r="I2" s="15">
+        <v>24.904214559387015</v>
+      </c>
+      <c r="J2" s="15">
+        <v>9.0996168582379937</v>
+      </c>
+      <c r="K2" s="15">
+        <v>1.0946907498629912</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0</v>
+      </c>
+      <c r="D3" s="15">
+        <v>22.304324028461899</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0</v>
+      </c>
+      <c r="I3" s="15">
+        <v>11.152162014231003</v>
+      </c>
+      <c r="J3" s="6">
+        <v>0</v>
+      </c>
+      <c r="K3" s="15">
+        <v>1.0946907498631973</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93247877-DA94-4205-8D39-1D56FD58FB79}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="19.5" customHeight="1">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A2" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="16">
+        <v>7977.7920136664497</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="16">
+        <v>239.16292974590033</v>
+      </c>
+      <c r="I2" s="16">
+        <v>5473.4144778987511</v>
+      </c>
+      <c r="J2" s="16">
+        <v>778.98782831519929</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="16">
+        <v>898.56929318810035</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="1" customFormat="1">
+      <c r="A3" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="16">
+        <v>2897.2880632073402</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="16">
+        <v>416.82682041426051</v>
+      </c>
+      <c r="I3" s="16">
+        <v>5473.4144778987802</v>
+      </c>
+      <c r="J3" s="16">
+        <v>772.15460175101907</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="16">
+        <v>591.07409780049966</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="1" customFormat="1">
+      <c r="A4" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="16">
+        <v>2815.2893444373199</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="16">
+        <v>3860.7730087550699</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="16">
+        <v>61.499039077520138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="1" customFormat="1">
+      <c r="A5" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="16">
+        <v>1141.1488362161001</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>720.90540251974971</v>
+      </c>
+      <c r="H5" s="2">
+        <v>307.49519538756999</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="1" customFormat="1">
+      <c r="A6" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1093.31625026692</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>47.832585949180157</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>23.916292974579846</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9357577D-0713-4E4B-A3BB-AD68DAA30E7A}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>2017</v>
+      </c>
+      <c r="B2">
+        <v>12.83</v>
+      </c>
+      <c r="C2">
+        <v>43.76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2022</v>
+      </c>
+      <c r="B3">
+        <v>73.209999999999994</v>
+      </c>
+      <c r="C3">
+        <v>130.43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D96294-59C6-4D17-8187-7AF364170473}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>2017</v>
+      </c>
+      <c r="B2">
+        <v>127.49</v>
+      </c>
+      <c r="C2">
+        <v>2175.3000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2022</v>
+      </c>
+      <c r="B3">
+        <v>456.77</v>
+      </c>
+      <c r="C3">
+        <v>2932.97</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D97205A8-3FDC-47E2-8EDC-6BA2438A1FD9}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>2017</v>
+      </c>
+      <c r="B2">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="C2">
+        <v>99.11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2022</v>
+      </c>
+      <c r="B3">
+        <v>68.45</v>
+      </c>
+      <c r="C3">
+        <v>171.12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D04D4904-CA5C-4DA0-9605-59863FBEE721}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>2017</v>
+      </c>
+      <c r="B2">
+        <v>2.77</v>
+      </c>
+      <c r="C2">
+        <v>42.26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2022</v>
+      </c>
+      <c r="B3">
+        <v>9.61</v>
+      </c>
+      <c r="C3">
+        <v>96.51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11E3DE1-1E50-44AB-B589-DEB337CC2043}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="24" customHeight="1">
+      <c r="A1" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="15">
+        <v>912</v>
+      </c>
+      <c r="D2" s="15">
+        <v>1095</v>
+      </c>
+      <c r="E2" s="15">
+        <f>AVERAGE(C2:D2)</f>
+        <v>1003.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="15">
+        <v>753</v>
+      </c>
+      <c r="D3" s="15">
+        <v>912</v>
+      </c>
+      <c r="E3" s="15">
+        <f t="shared" ref="E3:E23" si="0">AVERAGE(C3:D3)</f>
+        <v>832.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="15">
+        <v>850</v>
+      </c>
+      <c r="D4" s="15">
+        <v>1021</v>
+      </c>
+      <c r="E4" s="15">
+        <f t="shared" si="0"/>
+        <v>935.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="16">
+        <v>403</v>
+      </c>
+      <c r="D5" s="16">
+        <v>513</v>
+      </c>
+      <c r="E5" s="16">
+        <f t="shared" si="0"/>
+        <v>458</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="15">
+        <v>213</v>
+      </c>
+      <c r="D6" s="15">
+        <v>470</v>
+      </c>
+      <c r="E6" s="15">
+        <f t="shared" si="0"/>
+        <v>341.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="15">
+        <v>149</v>
+      </c>
+      <c r="D7" s="15">
+        <v>364</v>
+      </c>
+      <c r="E7" s="15">
+        <f t="shared" si="0"/>
+        <v>256.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="15">
+        <v>190</v>
+      </c>
+      <c r="D8" s="15">
+        <v>427</v>
+      </c>
+      <c r="E8" s="15">
+        <f t="shared" si="0"/>
+        <v>308.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="16">
+        <v>92</v>
+      </c>
+      <c r="D9" s="16">
+        <v>221</v>
+      </c>
+      <c r="E9" s="16">
+        <f t="shared" si="0"/>
+        <v>156.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="15">
+        <v>85</v>
+      </c>
+      <c r="D10" s="15">
+        <v>147</v>
+      </c>
+      <c r="E10" s="15">
+        <f t="shared" si="0"/>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="15">
+        <v>6.1</v>
+      </c>
+      <c r="D11" s="15">
+        <v>11</v>
+      </c>
+      <c r="E11" s="15">
+        <f t="shared" si="0"/>
+        <v>8.5500000000000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D12" s="16">
+        <v>6.4</v>
+      </c>
+      <c r="E12" s="16">
+        <f t="shared" si="0"/>
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="15">
+        <v>14</v>
+      </c>
+      <c r="D13" s="15">
+        <v>87</v>
+      </c>
+      <c r="E13" s="15">
+        <f t="shared" si="0"/>
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="15">
+        <v>27</v>
+      </c>
+      <c r="D14" s="15">
+        <v>122</v>
+      </c>
+      <c r="E14" s="15">
+        <f t="shared" si="0"/>
+        <v>74.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="16">
+        <v>23</v>
+      </c>
+      <c r="D15" s="16">
+        <v>82</v>
+      </c>
+      <c r="E15" s="16">
+        <f t="shared" si="0"/>
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="16">
+        <v>23</v>
+      </c>
+      <c r="D16" s="16">
+        <v>83</v>
+      </c>
+      <c r="E16" s="16">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="16">
+        <v>8</v>
+      </c>
+      <c r="D17" s="16">
+        <v>28</v>
+      </c>
+      <c r="E17" s="16">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="16">
+        <v>10</v>
+      </c>
+      <c r="D18" s="16">
+        <v>35</v>
+      </c>
+      <c r="E18" s="16">
+        <f t="shared" si="0"/>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="16">
+        <v>7.4</v>
+      </c>
+      <c r="D19" s="16">
+        <v>27</v>
+      </c>
+      <c r="E19" s="16">
+        <f t="shared" si="0"/>
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="16">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D20" s="16">
+        <v>34</v>
+      </c>
+      <c r="E20" s="16">
+        <f t="shared" si="0"/>
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="15">
+        <v>7.8</v>
+      </c>
+      <c r="D21" s="15">
+        <v>16</v>
+      </c>
+      <c r="E21" s="15">
+        <f t="shared" si="0"/>
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="15">
+        <v>13</v>
+      </c>
+      <c r="D22" s="15">
+        <v>23</v>
+      </c>
+      <c r="E22" s="15">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="15">
+        <v>12</v>
+      </c>
+      <c r="D23" s="15">
+        <v>21</v>
+      </c>
+      <c r="E23" s="15">
+        <f t="shared" si="0"/>
+        <v>16.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{154CC2AF-4989-4923-8B8E-B175B4ED0E63}">
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1392,636 +2628,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9357577D-0713-4E4B-A3BB-AD68DAA30E7A}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="19">
-        <v>2017</v>
-      </c>
-      <c r="C2" s="19">
-        <v>12.833099579242599</v>
-      </c>
-      <c r="D2" s="19">
-        <v>30</v>
-      </c>
-      <c r="E2" s="19">
-        <v>43.758765778401099</v>
-      </c>
-      <c r="F2" s="19">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="19">
-        <v>2022</v>
-      </c>
-      <c r="C3" s="19">
-        <v>73.211781206171096</v>
-      </c>
-      <c r="D3" s="19">
-        <v>56</v>
-      </c>
-      <c r="E3" s="19">
-        <v>130.434782608695</v>
-      </c>
-      <c r="F3" s="19">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="20">
-        <v>2017</v>
-      </c>
-      <c r="C4" s="16">
-        <v>127.490039840637</v>
-      </c>
-      <c r="D4" s="16">
-        <v>6</v>
-      </c>
-      <c r="E4" s="16">
-        <v>2175.2988047808699</v>
-      </c>
-      <c r="F4" s="16">
-        <f>100-D4</f>
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="20">
-        <v>2022</v>
-      </c>
-      <c r="C5" s="16">
-        <v>456.765530470709</v>
-      </c>
-      <c r="D5" s="16">
-        <v>16</v>
-      </c>
-      <c r="E5" s="16">
-        <v>2932.9718164379501</v>
-      </c>
-      <c r="F5" s="16">
-        <f>100-D5</f>
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="19">
-        <v>2017</v>
-      </c>
-      <c r="C6" s="15">
-        <v>16.399286987522199</v>
-      </c>
-      <c r="D6" s="15">
-        <v>17</v>
-      </c>
-      <c r="E6" s="15">
-        <v>99.108734402851994</v>
-      </c>
-      <c r="F6" s="15">
-        <f t="shared" ref="F6:F9" si="0">100-D6</f>
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="19">
-        <v>2022</v>
-      </c>
-      <c r="C7" s="15">
-        <v>68.449197860962499</v>
-      </c>
-      <c r="D7" s="15">
-        <v>40</v>
-      </c>
-      <c r="E7" s="15">
-        <v>171.12299465240599</v>
-      </c>
-      <c r="F7" s="15">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="20">
-        <v>2017</v>
-      </c>
-      <c r="C8" s="16">
-        <v>2.77456275720162</v>
-      </c>
-      <c r="D8" s="16">
-        <v>7</v>
-      </c>
-      <c r="E8" s="16">
-        <v>42.2590342078189</v>
-      </c>
-      <c r="F8" s="16">
-        <f t="shared" si="0"/>
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="20">
-        <v>2022</v>
-      </c>
-      <c r="C9" s="16">
-        <v>9.6064814814814596</v>
-      </c>
-      <c r="D9" s="16">
-        <v>10</v>
-      </c>
-      <c r="E9" s="16">
-        <v>96.5125064300411</v>
-      </c>
-      <c r="F9" s="16">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11E3DE1-1E50-44AB-B589-DEB337CC2043}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
-      <c r="A1" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="15">
-        <v>912</v>
-      </c>
-      <c r="D2" s="15">
-        <v>1095</v>
-      </c>
-      <c r="E2" s="15">
-        <f>AVERAGE(C2:D2)</f>
-        <v>1003.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="15">
-        <v>753</v>
-      </c>
-      <c r="D3" s="15">
-        <v>912</v>
-      </c>
-      <c r="E3" s="15">
-        <f t="shared" ref="E3:E23" si="0">AVERAGE(C3:D3)</f>
-        <v>832.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="15">
-        <v>850</v>
-      </c>
-      <c r="D4" s="15">
-        <v>1021</v>
-      </c>
-      <c r="E4" s="15">
-        <f t="shared" si="0"/>
-        <v>935.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="16">
-        <v>403</v>
-      </c>
-      <c r="D5" s="16">
-        <v>513</v>
-      </c>
-      <c r="E5" s="16">
-        <f t="shared" si="0"/>
-        <v>458</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="15">
-        <v>213</v>
-      </c>
-      <c r="D6" s="15">
-        <v>470</v>
-      </c>
-      <c r="E6" s="15">
-        <f t="shared" si="0"/>
-        <v>341.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="15">
-        <v>149</v>
-      </c>
-      <c r="D7" s="15">
-        <v>364</v>
-      </c>
-      <c r="E7" s="15">
-        <f t="shared" si="0"/>
-        <v>256.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="15">
-        <v>190</v>
-      </c>
-      <c r="D8" s="15">
-        <v>427</v>
-      </c>
-      <c r="E8" s="15">
-        <f t="shared" si="0"/>
-        <v>308.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="16">
-        <v>92</v>
-      </c>
-      <c r="D9" s="16">
-        <v>221</v>
-      </c>
-      <c r="E9" s="16">
-        <f t="shared" si="0"/>
-        <v>156.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="15">
-        <v>85</v>
-      </c>
-      <c r="D10" s="15">
-        <v>147</v>
-      </c>
-      <c r="E10" s="15">
-        <f t="shared" si="0"/>
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="15">
-        <v>6.1</v>
-      </c>
-      <c r="D11" s="15">
-        <v>11</v>
-      </c>
-      <c r="E11" s="15">
-        <f t="shared" si="0"/>
-        <v>8.5500000000000007</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="16">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="D12" s="16">
-        <v>6.4</v>
-      </c>
-      <c r="E12" s="16">
-        <f t="shared" si="0"/>
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="15">
-        <v>14</v>
-      </c>
-      <c r="D13" s="15">
-        <v>87</v>
-      </c>
-      <c r="E13" s="15">
-        <f t="shared" si="0"/>
-        <v>50.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="15">
-        <v>27</v>
-      </c>
-      <c r="D14" s="15">
-        <v>122</v>
-      </c>
-      <c r="E14" s="15">
-        <f t="shared" si="0"/>
-        <v>74.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="16">
-        <v>23</v>
-      </c>
-      <c r="D15" s="16">
-        <v>82</v>
-      </c>
-      <c r="E15" s="16">
-        <f t="shared" si="0"/>
-        <v>52.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="16">
-        <v>23</v>
-      </c>
-      <c r="D16" s="16">
-        <v>83</v>
-      </c>
-      <c r="E16" s="16">
-        <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="16">
-        <v>8</v>
-      </c>
-      <c r="D17" s="16">
-        <v>28</v>
-      </c>
-      <c r="E17" s="16">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="16">
-        <v>10</v>
-      </c>
-      <c r="D18" s="16">
-        <v>35</v>
-      </c>
-      <c r="E18" s="16">
-        <f t="shared" si="0"/>
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="16">
-        <v>7.4</v>
-      </c>
-      <c r="D19" s="16">
-        <v>27</v>
-      </c>
-      <c r="E19" s="16">
-        <f t="shared" si="0"/>
-        <v>17.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="16">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="D20" s="16">
-        <v>34</v>
-      </c>
-      <c r="E20" s="16">
-        <f t="shared" si="0"/>
-        <v>21.6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="15">
-        <v>7.8</v>
-      </c>
-      <c r="D21" s="15">
-        <v>16</v>
-      </c>
-      <c r="E21" s="15">
-        <f t="shared" si="0"/>
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="15">
-        <v>13</v>
-      </c>
-      <c r="D22" s="15">
-        <v>23</v>
-      </c>
-      <c r="E22" s="15">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="15">
-        <v>12</v>
-      </c>
-      <c r="D23" s="15">
-        <v>21</v>
-      </c>
-      <c r="E23" s="15">
-        <f t="shared" si="0"/>
-        <v>16.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010098970033F315F542A2D9640B7CC02236" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94449e8ff35cec47b43afd2e381d9e90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3" xmlns:ns3="c8670835-afc4-4376-8ae0-1ffed5b27e6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7f21ad7dc1dad656b5a5a7699096a32" ns2:_="" ns3:_="">
     <xsd:import namespace="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
@@ -2262,17 +2880,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2283,11 +2890,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F87B3EE-5415-410A-AC93-A1F746B20A3D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10B2F4FE-1C4B-46BF-9235-53580805D83F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10B2F4FE-1C4B-46BF-9235-53580805D83F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F87B3EE-5415-410A-AC93-A1F746B20A3D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/02_Inputs/Data/Charts/Module 3 - Dasasets for Charts.xlsx
+++ b/02_Inputs/Data/Charts/Module 3 - Dasasets for Charts.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="714" documentId="11_86B3BED064903DA954D0E649743742B46DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0942F98D-A3CC-456D-9EF2-8CA29F61922A}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\fschi\undp\dsc-energy-academy-data\02_Inputs\Data\Charts\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3029BF1-351C-436C-8E44-3776D9C55FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M3_C2_7" sheetId="1" r:id="rId1"/>
@@ -40,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="80">
   <si>
     <t>Sector</t>
   </si>
@@ -277,13 +282,16 @@
   </si>
   <si>
     <t>Neodymium</t>
+  </si>
+  <si>
+    <t>Lithium</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -868,12 +876,12 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="35.42578125" customWidth="1"/>
+    <col min="1" max="1" width="35.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -887,7 +895,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -901,7 +909,7 @@
         <v>3956.6954926624699</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -915,7 +923,7 @@
         <v>-7085.0803633822497</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="45.75">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -929,7 +937,7 @@
         <v>-9842.1121593291391</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="30.75">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -943,7 +951,7 @@
         <v>-171.20992772291899</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="30.75">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -957,7 +965,7 @@
         <v>9316.0741323084094</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="45.75">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -971,7 +979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
@@ -985,7 +993,7 @@
         <v>4982.6206906592097</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -999,7 +1007,7 @@
         <v>-2114.6888830654502</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
@@ -1013,7 +1021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="30.75">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -1027,7 +1035,7 @@
         <v>-2090.9932715078698</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
@@ -1041,7 +1049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="76.5">
+    <row r="13" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -1055,7 +1063,7 @@
         <v>799.87133851619103</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
@@ -1069,7 +1077,7 @@
         <v>8082.3226238773696</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="8" t="s">
         <v>14</v>
       </c>
@@ -1091,17 +1099,17 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3416D971-AC8D-4ECA-A9B5-B8058DC8EE89}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="5" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" customWidth="1"/>
+    <col min="3" max="3" width="20.3984375" customWidth="1"/>
+    <col min="4" max="4" width="28.73046875" customWidth="1"/>
+    <col min="5" max="5" width="31.1328125" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="17" t="s">
         <v>72</v>
       </c>
@@ -1121,7 +1129,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="28" t="s">
         <v>77</v>
       </c>
@@ -1141,7 +1149,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="28" t="s">
         <v>77</v>
       </c>
@@ -1161,7 +1169,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="29" t="s">
         <v>21</v>
       </c>
@@ -1182,7 +1190,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="29" t="s">
         <v>21</v>
       </c>
@@ -1203,7 +1211,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="28" t="s">
         <v>19</v>
       </c>
@@ -1224,7 +1232,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="28" t="s">
         <v>19</v>
       </c>
@@ -1245,7 +1253,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="29" t="s">
         <v>78</v>
       </c>
@@ -1266,7 +1274,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="29" t="s">
         <v>78</v>
       </c>
@@ -1298,14 +1306,14 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23.140625" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.1328125" customWidth="1"/>
+    <col min="2" max="2" width="15.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19.5" customHeight="1">
+    <row r="1" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="14" t="s">
         <v>15</v>
       </c>
@@ -1334,13 +1342,13 @@
         <v>23</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="K1" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="30" t="s">
         <v>26</v>
       </c>
@@ -1375,7 +1383,7 @@
         <v>1.0946907498629912</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="30" t="s">
         <v>26</v>
       </c>
@@ -1421,15 +1429,15 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.1328125" customWidth="1"/>
+    <col min="2" max="2" width="23.1328125" customWidth="1"/>
+    <col min="3" max="3" width="15.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19.5" customHeight="1">
+    <row r="1" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1461,13 +1469,13 @@
         <v>23</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L1" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="31" t="s">
         <v>29</v>
       </c>
@@ -1505,7 +1513,7 @@
         <v>898.56929318810035</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1">
+    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A3" s="31" t="s">
         <v>29</v>
       </c>
@@ -1543,7 +1551,7 @@
         <v>591.07409780049966</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1">
+    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="31" t="s">
         <v>29</v>
       </c>
@@ -1581,7 +1589,7 @@
         <v>61.499039077520138</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1">
+    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A5" s="31" t="s">
         <v>29</v>
       </c>
@@ -1619,7 +1627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="1" customFormat="1">
+    <row r="6" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A6" s="31" t="s">
         <v>29</v>
       </c>
@@ -1668,17 +1676,17 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="5" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" customWidth="1"/>
+    <col min="3" max="3" width="20.3984375" customWidth="1"/>
+    <col min="4" max="4" width="28.73046875" customWidth="1"/>
+    <col min="5" max="5" width="31.1328125" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="32" t="s">
         <v>36</v>
       </c>
@@ -1689,7 +1697,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>2017</v>
       </c>
@@ -1700,7 +1708,7 @@
         <v>43.76</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2022</v>
       </c>
@@ -1722,17 +1730,17 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="5" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" customWidth="1"/>
+    <col min="3" max="3" width="20.3984375" customWidth="1"/>
+    <col min="4" max="4" width="28.73046875" customWidth="1"/>
+    <col min="5" max="5" width="31.1328125" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="32" t="s">
         <v>36</v>
       </c>
@@ -1743,7 +1751,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>2017</v>
       </c>
@@ -1754,7 +1762,7 @@
         <v>2175.3000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2022</v>
       </c>
@@ -1776,17 +1784,17 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="5" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" customWidth="1"/>
+    <col min="3" max="3" width="20.3984375" customWidth="1"/>
+    <col min="4" max="4" width="28.73046875" customWidth="1"/>
+    <col min="5" max="5" width="31.1328125" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="32" t="s">
         <v>36</v>
       </c>
@@ -1797,7 +1805,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>2017</v>
       </c>
@@ -1808,7 +1816,7 @@
         <v>99.11</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2022</v>
       </c>
@@ -1830,17 +1838,17 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="5" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" customWidth="1"/>
+    <col min="3" max="3" width="20.3984375" customWidth="1"/>
+    <col min="4" max="4" width="28.73046875" customWidth="1"/>
+    <col min="5" max="5" width="31.1328125" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="32" t="s">
         <v>36</v>
       </c>
@@ -1851,7 +1859,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>2017</v>
       </c>
@@ -1862,7 +1870,7 @@
         <v>42.26</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2022</v>
       </c>
@@ -1884,13 +1892,13 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="17" t="s">
         <v>39</v>
       </c>
@@ -1907,7 +1915,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="24" t="s">
         <v>44</v>
       </c>
@@ -1925,7 +1933,7 @@
         <v>1003.5</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="24" t="s">
         <v>44</v>
       </c>
@@ -1943,7 +1951,7 @@
         <v>832.5</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="24" t="s">
         <v>44</v>
       </c>
@@ -1961,7 +1969,7 @@
         <v>935.5</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="18" t="s">
         <v>35</v>
       </c>
@@ -1979,7 +1987,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="24" t="s">
         <v>44</v>
       </c>
@@ -1997,7 +2005,7 @@
         <v>341.5</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="24" t="s">
         <v>44</v>
       </c>
@@ -2015,7 +2023,7 @@
         <v>256.5</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="24" t="s">
         <v>44</v>
       </c>
@@ -2033,7 +2041,7 @@
         <v>308.5</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="18" t="s">
         <v>35</v>
       </c>
@@ -2051,7 +2059,7 @@
         <v>156.5</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="25" t="s">
         <v>53</v>
       </c>
@@ -2069,7 +2077,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="25" t="s">
         <v>53</v>
       </c>
@@ -2087,7 +2095,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="21" t="s">
         <v>56</v>
       </c>
@@ -2105,7 +2113,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="24" t="s">
         <v>58</v>
       </c>
@@ -2123,7 +2131,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="24" t="s">
         <v>58</v>
       </c>
@@ -2141,7 +2149,7 @@
         <v>74.5</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="26" t="s">
         <v>61</v>
       </c>
@@ -2159,7 +2167,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="27" t="s">
         <v>61</v>
       </c>
@@ -2177,7 +2185,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="27" t="s">
         <v>61</v>
       </c>
@@ -2195,7 +2203,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="27" t="s">
         <v>61</v>
       </c>
@@ -2213,7 +2221,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="27" t="s">
         <v>61</v>
       </c>
@@ -2231,7 +2239,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="27" t="s">
         <v>61</v>
       </c>
@@ -2249,7 +2257,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="24" t="s">
         <v>68</v>
       </c>
@@ -2267,7 +2275,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="24" t="s">
         <v>68</v>
       </c>
@@ -2285,7 +2293,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="24" t="s">
         <v>68</v>
       </c>
@@ -2311,15 +2319,15 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{154CC2AF-4989-4923-8B8E-B175B4ED0E63}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.1328125" customWidth="1"/>
+    <col min="2" max="2" width="23.1328125" customWidth="1"/>
+    <col min="3" max="3" width="15.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19.5" customHeight="1">
+    <row r="1" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -2357,7 +2365,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="30" t="s">
         <v>11</v>
       </c>
@@ -2395,7 +2403,7 @@
         <v>1.0946907498629912</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="30" t="s">
         <v>11</v>
       </c>
@@ -2433,7 +2441,7 @@
         <v>1.0946907498631973</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
+    <row r="4" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="31" t="s">
         <v>29</v>
       </c>
@@ -2471,7 +2479,7 @@
         <v>898.56929318810035</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1">
+    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A5" s="31" t="s">
         <v>29</v>
       </c>
@@ -2509,7 +2517,7 @@
         <v>591.07409780049966</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="1" customFormat="1">
+    <row r="6" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A6" s="31" t="s">
         <v>29</v>
       </c>
@@ -2547,7 +2555,7 @@
         <v>61.499039077520138</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="1" customFormat="1">
+    <row r="7" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A7" s="31" t="s">
         <v>29</v>
       </c>
@@ -2585,7 +2593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="1" customFormat="1">
+    <row r="8" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A8" s="31" t="s">
         <v>29</v>
       </c>
@@ -2629,14 +2637,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2881,22 +2887,50 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10B2F4FE-1C4B-46BF-9235-53580805D83F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75B04653-368D-4396-B429-F735F1D4ABC0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F87B3EE-5415-410A-AC93-A1F746B20A3D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F87B3EE-5415-410A-AC93-A1F746B20A3D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
+    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75B04653-368D-4396-B429-F735F1D4ABC0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10B2F4FE-1C4B-46BF-9235-53580805D83F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
+    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/02_Inputs/Data/Charts/Module 3 - Dasasets for Charts.xlsx
+++ b/02_Inputs/Data/Charts/Module 3 - Dasasets for Charts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29019"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\fschi\undp\dsc-energy-academy-data\02_Inputs\Data\Charts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/SEHCoreTeam/Shared Documents/General/04. Sustainable Energy Academy/SEA Charts and Infographics/SEA - Charts/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3029BF1-351C-436C-8E44-3776D9C55FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="769" documentId="11_86B3BED064903DA954D0E649743742B46DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89A3C398-822E-41AC-8077-6EB79B608FD7}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M3_C2_7" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,11 @@
     <sheet name="M3_C3_12_2" sheetId="7" r:id="rId5"/>
     <sheet name="M3_C3_12_3" sheetId="8" r:id="rId6"/>
     <sheet name="M3_C3_12_4" sheetId="9" r:id="rId7"/>
-    <sheet name="M3_C3_15" sheetId="4" r:id="rId8"/>
-    <sheet name="(Legacy) M3_C3_11" sheetId="6" r:id="rId9"/>
-    <sheet name="(Legacy) M3_C2_12" sheetId="10" r:id="rId10"/>
+    <sheet name="M3_C3_12_5" sheetId="11" r:id="rId8"/>
+    <sheet name="M3_C3_12_6" sheetId="12" r:id="rId9"/>
+    <sheet name="M3_C3_15" sheetId="4" r:id="rId10"/>
+    <sheet name="(Legacy) M3_C3_11" sheetId="6" r:id="rId11"/>
+    <sheet name="(Legacy) M3_C2_12" sheetId="10" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="85">
   <si>
     <t>Sector</t>
   </si>
@@ -119,150 +121,168 @@
     <t>Manganese</t>
   </si>
   <si>
+    <t>Lithium</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Kilograms per vehicle</t>
+  </si>
+  <si>
+    <t>Electric car</t>
+  </si>
+  <si>
+    <t>Conventional car</t>
+  </si>
+  <si>
+    <t>Power generation</t>
+  </si>
+  <si>
+    <t>Kilograms per megawatt</t>
+  </si>
+  <si>
+    <t>Offshore wind</t>
+  </si>
+  <si>
+    <t>Onshore wind</t>
+  </si>
+  <si>
+    <t>Solar PV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coal </t>
+  </si>
+  <si>
+    <t>Natural gas</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Total use</t>
+  </si>
+  <si>
+    <t>Energy Technologies</t>
+  </si>
+  <si>
+    <t>Other uses</t>
+  </si>
+  <si>
+    <t>APS</t>
+  </si>
+  <si>
+    <t>NZE</t>
+  </si>
+  <si>
+    <t>Total increase in demand (compared to 2024)</t>
+  </si>
+  <si>
+    <t>Share for energy technologies (%)</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Hard coal</t>
+  </si>
+  <si>
+    <t>PC, without CCS</t>
+  </si>
+  <si>
+    <t>IGCC, without CCS</t>
+  </si>
+  <si>
+    <t>SC, without CCS</t>
+  </si>
+  <si>
+    <t>NGCC, without CCS</t>
+  </si>
+  <si>
+    <t>PC, with CCS</t>
+  </si>
+  <si>
+    <t>IGCC, with CCS</t>
+  </si>
+  <si>
+    <t>SC, with CCS</t>
+  </si>
+  <si>
+    <t>NGCC, with CCS</t>
+  </si>
+  <si>
+    <t>Hydro</t>
+  </si>
+  <si>
+    <t>660 MW</t>
+  </si>
+  <si>
+    <t>360 MW</t>
+  </si>
+  <si>
+    <t>Nuclear</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>CSP</t>
+  </si>
+  <si>
+    <t>tower</t>
+  </si>
+  <si>
+    <t>trough</t>
+  </si>
+  <si>
+    <t>PV</t>
+  </si>
+  <si>
+    <t>poly-Si, ground-mounted</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> poly-Si, roof-mounted</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CdTe, ground-mounted</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CdTe, roof-mounted</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CIGS, ground-mounted</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CIGS, roof-mounted</t>
+  </si>
+  <si>
+    <t>Wind</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> onshore</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> offshore, concrete foundation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> offshore, steel foundation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lithium </t>
   </si>
   <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>Kilograms per vehicle</t>
-  </si>
-  <si>
-    <t>Electric car</t>
-  </si>
-  <si>
-    <t>Conventional car</t>
-  </si>
-  <si>
-    <t>Power generation</t>
-  </si>
-  <si>
-    <t>Kilograms per megawatt</t>
-  </si>
-  <si>
-    <t>Offshore wind</t>
-  </si>
-  <si>
-    <t>Onshore wind</t>
-  </si>
-  <si>
-    <t>Solar PV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coal </t>
-  </si>
-  <si>
-    <t>Natural gas</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Clean energy</t>
-  </si>
-  <si>
-    <t>Other uses</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Hard coal</t>
-  </si>
-  <si>
-    <t>PC, without CCS</t>
-  </si>
-  <si>
-    <t>IGCC, without CCS</t>
-  </si>
-  <si>
-    <t>SC, without CCS</t>
-  </si>
-  <si>
-    <t>NGCC, without CCS</t>
-  </si>
-  <si>
-    <t>PC, with CCS</t>
-  </si>
-  <si>
-    <t>IGCC, with CCS</t>
-  </si>
-  <si>
-    <t>SC, with CCS</t>
-  </si>
-  <si>
-    <t>NGCC, with CCS</t>
-  </si>
-  <si>
-    <t>Hydro</t>
-  </si>
-  <si>
-    <t>660 MW</t>
-  </si>
-  <si>
-    <t>360 MW</t>
-  </si>
-  <si>
-    <t>Nuclear</t>
-  </si>
-  <si>
-    <t>average</t>
-  </si>
-  <si>
-    <t>CSP</t>
-  </si>
-  <si>
-    <t>tower</t>
-  </si>
-  <si>
-    <t>trough</t>
-  </si>
-  <si>
-    <t>PV</t>
-  </si>
-  <si>
-    <t>poly-Si, ground-mounted</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> poly-Si, roof-mounted</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CdTe, ground-mounted</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CdTe, roof-mounted</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CIGS, ground-mounted</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CIGS, roof-mounted</t>
-  </si>
-  <si>
-    <t>Wind</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> onshore</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> offshore, concrete foundation</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> offshore, steel foundation</t>
-  </si>
-  <si>
     <t>Mineral</t>
   </si>
   <si>
@@ -282,16 +302,13 @@
   </si>
   <si>
     <t>Neodymium</t>
-  </si>
-  <si>
-    <t>Lithium</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,8 +337,15 @@
       <name val="Aptos Narrow"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -343,6 +367,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -442,10 +472,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -532,10 +563,28 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -876,12 +925,12 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="35.3984375" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -895,7 +944,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -909,7 +958,7 @@
         <v>3956.6954926624699</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -923,7 +972,7 @@
         <v>-7085.0803633822497</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -937,7 +986,7 @@
         <v>-9842.1121593291391</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -951,7 +1000,7 @@
         <v>-171.20992772291899</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -965,7 +1014,7 @@
         <v>9316.0741323084094</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -979,7 +1028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
@@ -993,7 +1042,7 @@
         <v>4982.6206906592097</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -1007,7 +1056,7 @@
         <v>-2114.6888830654502</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
@@ -1021,7 +1070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -1035,7 +1084,7 @@
         <v>-2090.9932715078698</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
@@ -1049,7 +1098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" ht="28.5">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -1063,7 +1112,7 @@
         <v>799.87133851619103</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4">
       <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
@@ -1077,7 +1126,7 @@
         <v>8082.3226238773696</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4">
       <c r="A15" s="8" t="s">
         <v>14</v>
       </c>
@@ -1097,41 +1146,791 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11E3DE1-1E50-44AB-B589-DEB337CC2043}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="24" customHeight="1">
+      <c r="A1" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="15">
+        <v>912</v>
+      </c>
+      <c r="D2" s="15">
+        <v>1095</v>
+      </c>
+      <c r="E2" s="15">
+        <f>AVERAGE(C2:D2)</f>
+        <v>1003.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="15">
+        <v>753</v>
+      </c>
+      <c r="D3" s="15">
+        <v>912</v>
+      </c>
+      <c r="E3" s="15">
+        <f t="shared" ref="E3:E23" si="0">AVERAGE(C3:D3)</f>
+        <v>832.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="15">
+        <v>850</v>
+      </c>
+      <c r="D4" s="15">
+        <v>1021</v>
+      </c>
+      <c r="E4" s="15">
+        <f t="shared" si="0"/>
+        <v>935.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="16">
+        <v>403</v>
+      </c>
+      <c r="D5" s="16">
+        <v>513</v>
+      </c>
+      <c r="E5" s="16">
+        <f t="shared" si="0"/>
+        <v>458</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="15">
+        <v>213</v>
+      </c>
+      <c r="D6" s="15">
+        <v>470</v>
+      </c>
+      <c r="E6" s="15">
+        <f t="shared" si="0"/>
+        <v>341.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="15">
+        <v>149</v>
+      </c>
+      <c r="D7" s="15">
+        <v>364</v>
+      </c>
+      <c r="E7" s="15">
+        <f t="shared" si="0"/>
+        <v>256.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="15">
+        <v>190</v>
+      </c>
+      <c r="D8" s="15">
+        <v>427</v>
+      </c>
+      <c r="E8" s="15">
+        <f t="shared" si="0"/>
+        <v>308.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="16">
+        <v>92</v>
+      </c>
+      <c r="D9" s="16">
+        <v>221</v>
+      </c>
+      <c r="E9" s="16">
+        <f t="shared" si="0"/>
+        <v>156.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="15">
+        <v>85</v>
+      </c>
+      <c r="D10" s="15">
+        <v>147</v>
+      </c>
+      <c r="E10" s="15">
+        <f t="shared" si="0"/>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="15">
+        <v>6.1</v>
+      </c>
+      <c r="D11" s="15">
+        <v>11</v>
+      </c>
+      <c r="E11" s="15">
+        <f t="shared" si="0"/>
+        <v>8.5500000000000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D12" s="16">
+        <v>6.4</v>
+      </c>
+      <c r="E12" s="16">
+        <f t="shared" si="0"/>
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="15">
+        <v>14</v>
+      </c>
+      <c r="D13" s="15">
+        <v>87</v>
+      </c>
+      <c r="E13" s="15">
+        <f t="shared" si="0"/>
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="15">
+        <v>27</v>
+      </c>
+      <c r="D14" s="15">
+        <v>122</v>
+      </c>
+      <c r="E14" s="15">
+        <f t="shared" si="0"/>
+        <v>74.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="16">
+        <v>23</v>
+      </c>
+      <c r="D15" s="16">
+        <v>82</v>
+      </c>
+      <c r="E15" s="16">
+        <f t="shared" si="0"/>
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="16">
+        <v>23</v>
+      </c>
+      <c r="D16" s="16">
+        <v>83</v>
+      </c>
+      <c r="E16" s="16">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="16">
+        <v>8</v>
+      </c>
+      <c r="D17" s="16">
+        <v>28</v>
+      </c>
+      <c r="E17" s="16">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="16">
+        <v>10</v>
+      </c>
+      <c r="D18" s="16">
+        <v>35</v>
+      </c>
+      <c r="E18" s="16">
+        <f t="shared" si="0"/>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="16">
+        <v>7.4</v>
+      </c>
+      <c r="D19" s="16">
+        <v>27</v>
+      </c>
+      <c r="E19" s="16">
+        <f t="shared" si="0"/>
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="16">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D20" s="16">
+        <v>34</v>
+      </c>
+      <c r="E20" s="16">
+        <f t="shared" si="0"/>
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="15">
+        <v>7.8</v>
+      </c>
+      <c r="D21" s="15">
+        <v>16</v>
+      </c>
+      <c r="E21" s="15">
+        <f t="shared" si="0"/>
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="15">
+        <v>13</v>
+      </c>
+      <c r="D22" s="15">
+        <v>23</v>
+      </c>
+      <c r="E22" s="15">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="15">
+        <v>12</v>
+      </c>
+      <c r="D23" s="15">
+        <v>21</v>
+      </c>
+      <c r="E23" s="15">
+        <f t="shared" si="0"/>
+        <v>16.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{154CC2AF-4989-4923-8B8E-B175B4ED0E63}">
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="19.5" customHeight="1">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="15">
+        <v>66.297208538587796</v>
+      </c>
+      <c r="E2" s="15">
+        <v>53.160919540229202</v>
+      </c>
+      <c r="F2" s="15">
+        <v>13.067870826491003</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0</v>
+      </c>
+      <c r="H2" s="15">
+        <v>39.340448823207993</v>
+      </c>
+      <c r="I2" s="6">
+        <v>0</v>
+      </c>
+      <c r="J2" s="15">
+        <v>24.904214559387015</v>
+      </c>
+      <c r="K2" s="15">
+        <v>9.0996168582379937</v>
+      </c>
+      <c r="L2" s="15">
+        <v>1.0946907498629912</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0</v>
+      </c>
+      <c r="E3" s="15">
+        <v>22.304324028461899</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0</v>
+      </c>
+      <c r="J3" s="15">
+        <v>11.152162014231003</v>
+      </c>
+      <c r="K3" s="6">
+        <v>0</v>
+      </c>
+      <c r="L3" s="15">
+        <v>1.0946907498631973</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A4" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="16">
+        <v>7977.7920136664497</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="16">
+        <v>239.16292974590033</v>
+      </c>
+      <c r="I4" s="16">
+        <v>5473.4144778987511</v>
+      </c>
+      <c r="J4" s="16">
+        <v>778.98782831519929</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="16">
+        <v>898.56929318810035</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="1" customFormat="1">
+      <c r="A5" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="16">
+        <v>2897.2880632073402</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="16">
+        <v>416.82682041426051</v>
+      </c>
+      <c r="I5" s="16">
+        <v>5473.4144778987802</v>
+      </c>
+      <c r="J5" s="16">
+        <v>772.15460175101907</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="16">
+        <v>591.07409780049966</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="1" customFormat="1">
+      <c r="A6" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="16">
+        <v>2815.2893444373199</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="16">
+        <v>3860.7730087550699</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="16">
+        <v>61.499039077520138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="1" customFormat="1">
+      <c r="A7" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="16">
+        <v>1141.1488362161001</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>720.90540251974971</v>
+      </c>
+      <c r="H7" s="2">
+        <v>307.49519538756999</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="1" customFormat="1">
+      <c r="A8" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1093.31625026692</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>47.832585949180157</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>23.916292974579846</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3416D971-AC8D-4ECA-A9B5-B8058DC8EE89}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.59765625" customWidth="1"/>
-    <col min="3" max="3" width="20.3984375" customWidth="1"/>
-    <col min="4" max="4" width="28.73046875" customWidth="1"/>
-    <col min="5" max="5" width="31.1328125" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6">
       <c r="A1" s="17" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>36</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="28" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B2" s="19">
         <v>2017</v>
@@ -1149,9 +1948,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6">
       <c r="A3" s="28" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B3" s="19">
         <v>2022</v>
@@ -1169,7 +1968,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6">
       <c r="A4" s="29" t="s">
         <v>21</v>
       </c>
@@ -1190,7 +1989,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6">
       <c r="A5" s="29" t="s">
         <v>21</v>
       </c>
@@ -1211,7 +2010,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6">
       <c r="A6" s="28" t="s">
         <v>19</v>
       </c>
@@ -1232,7 +2031,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6">
       <c r="A7" s="28" t="s">
         <v>19</v>
       </c>
@@ -1253,9 +2052,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6">
       <c r="A8" s="29" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B8" s="20">
         <v>2017</v>
@@ -1274,9 +2073,9 @@
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6">
       <c r="A9" s="29" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B9" s="20">
         <v>2022</v>
@@ -1306,14 +2105,14 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="23.1328125" customWidth="1"/>
-    <col min="2" max="2" width="15.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="19.5" customHeight="1">
       <c r="A1" s="14" t="s">
         <v>15</v>
       </c>
@@ -1342,13 +2141,13 @@
         <v>23</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="K1" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11">
       <c r="A2" s="30" t="s">
         <v>26</v>
       </c>
@@ -1383,7 +2182,7 @@
         <v>1.0946907498629912</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11">
       <c r="A3" s="30" t="s">
         <v>26</v>
       </c>
@@ -1429,15 +2228,15 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19.1328125" customWidth="1"/>
-    <col min="2" max="2" width="23.1328125" customWidth="1"/>
-    <col min="3" max="3" width="15.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" ht="19.5" customHeight="1">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1469,13 +2268,13 @@
         <v>23</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="L1" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="31" t="s">
         <v>29</v>
       </c>
@@ -1513,7 +2312,7 @@
         <v>898.56929318810035</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" s="1" customFormat="1">
       <c r="A3" s="31" t="s">
         <v>29</v>
       </c>
@@ -1551,7 +2350,7 @@
         <v>591.07409780049966</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" s="1" customFormat="1">
       <c r="A4" s="31" t="s">
         <v>29</v>
       </c>
@@ -1589,7 +2388,7 @@
         <v>61.499039077520138</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" s="1" customFormat="1">
       <c r="A5" s="31" t="s">
         <v>29</v>
       </c>
@@ -1627,7 +2426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" s="1" customFormat="1">
       <c r="A6" s="31" t="s">
         <v>29</v>
       </c>
@@ -1675,18 +2474,19 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.59765625" customWidth="1"/>
-    <col min="3" max="3" width="20.3984375" customWidth="1"/>
-    <col min="4" max="4" width="28.73046875" customWidth="1"/>
-    <col min="5" max="5" width="31.1328125" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="29.25">
       <c r="A1" s="32" t="s">
         <v>36</v>
       </c>
@@ -1696,27 +2496,101 @@
       <c r="C1" s="32" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2">
-        <v>2017</v>
-      </c>
-      <c r="B2">
-        <v>12.83</v>
-      </c>
-      <c r="C2">
-        <v>43.76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3">
-        <v>2022</v>
-      </c>
-      <c r="B3">
-        <v>73.209999999999994</v>
-      </c>
-      <c r="C3">
-        <v>130.43</v>
+      <c r="D1" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="32"/>
+      <c r="H1" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="35">
+        <v>2024</v>
+      </c>
+      <c r="B2" s="35">
+        <v>26.7412140575079</v>
+      </c>
+      <c r="C2" s="35">
+        <v>7.6996805111820796</v>
+      </c>
+      <c r="D2" s="35">
+        <v>19.04153354632582</v>
+      </c>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="37">
+        <f>C2/B2</f>
+        <v>0.28793309438470716</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="35">
+        <v>2030</v>
+      </c>
+      <c r="B3" s="35">
+        <v>31.246006389776301</v>
+      </c>
+      <c r="C3" s="35">
+        <v>10.894568690095801</v>
+      </c>
+      <c r="D3" s="35">
+        <v>20.351437699680503</v>
+      </c>
+      <c r="E3" s="35">
+        <v>32.587859424920097</v>
+      </c>
+      <c r="F3" s="35">
+        <v>34.4089456869009</v>
+      </c>
+      <c r="G3" s="35"/>
+      <c r="H3" s="36">
+        <f>B3/B2</f>
+        <v>1.1684587813620089</v>
+      </c>
+      <c r="I3" s="37">
+        <f>C3/B3</f>
+        <v>0.34867075664621594</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="35">
+        <v>2040</v>
+      </c>
+      <c r="B4" s="35">
+        <v>34.089456869009503</v>
+      </c>
+      <c r="C4" s="35">
+        <v>12.108626198083</v>
+      </c>
+      <c r="D4" s="35">
+        <v>21.980830670926501</v>
+      </c>
+      <c r="E4" s="35">
+        <v>36.741214057507896</v>
+      </c>
+      <c r="F4" s="35">
+        <v>39.520766773162997</v>
+      </c>
+      <c r="G4" s="35"/>
+      <c r="H4" s="36">
+        <f>B4/B2</f>
+        <v>1.2747909199522114</v>
+      </c>
+      <c r="I4" s="37">
+        <f>C4/B4</f>
+        <v>0.35520149953139535</v>
       </c>
     </row>
   </sheetData>
@@ -1729,18 +2603,19 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.59765625" customWidth="1"/>
-    <col min="3" max="3" width="20.3984375" customWidth="1"/>
-    <col min="4" max="4" width="28.73046875" customWidth="1"/>
-    <col min="5" max="5" width="31.1328125" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="29.25">
       <c r="A1" s="32" t="s">
         <v>36</v>
       </c>
@@ -1750,27 +2625,101 @@
       <c r="C1" s="32" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2">
-        <v>2017</v>
-      </c>
-      <c r="B2">
-        <v>127.49</v>
-      </c>
-      <c r="C2">
-        <v>2175.3000000000002</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3">
-        <v>2022</v>
-      </c>
-      <c r="B3">
-        <v>456.77</v>
-      </c>
-      <c r="C3">
-        <v>2932.97</v>
+      <c r="D1" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="32"/>
+      <c r="H1" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="35">
+        <v>2024</v>
+      </c>
+      <c r="B2" s="35">
+        <v>0.2006389776357824</v>
+      </c>
+      <c r="C2" s="35">
+        <v>0.1201277955271552</v>
+      </c>
+      <c r="D2" s="35">
+        <v>8.0511182108627205E-2</v>
+      </c>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="37">
+        <f>C2/B2</f>
+        <v>0.59872611464967584</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="35">
+        <v>2030</v>
+      </c>
+      <c r="B3" s="35">
+        <v>0.46006389776357604</v>
+      </c>
+      <c r="C3" s="35">
+        <v>0.36932907348242799</v>
+      </c>
+      <c r="D3" s="35">
+        <v>9.0734824281148013E-2</v>
+      </c>
+      <c r="E3" s="35">
+        <v>0.51118210862619595</v>
+      </c>
+      <c r="F3" s="35">
+        <v>0.70798722044728002</v>
+      </c>
+      <c r="G3" s="35"/>
+      <c r="H3" s="36">
+        <f>B3/B2</f>
+        <v>2.2929936305732412</v>
+      </c>
+      <c r="I3" s="37">
+        <f>C3/B3</f>
+        <v>0.80277777777778148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="35">
+        <v>2040</v>
+      </c>
+      <c r="B4" s="35">
+        <v>0.92523961661341603</v>
+      </c>
+      <c r="C4" s="35">
+        <v>0.80127795527156398</v>
+      </c>
+      <c r="D4" s="35">
+        <v>0.12396166134185208</v>
+      </c>
+      <c r="E4" s="35">
+        <v>1.2102236421725201</v>
+      </c>
+      <c r="F4" s="35">
+        <v>1.55399361022364</v>
+      </c>
+      <c r="G4" s="35"/>
+      <c r="H4" s="36">
+        <f>B4/B2</f>
+        <v>4.6114649681528617</v>
+      </c>
+      <c r="I4" s="37">
+        <f>C4/B4</f>
+        <v>0.86602209944751452</v>
       </c>
     </row>
   </sheetData>
@@ -1783,18 +2732,19 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.59765625" customWidth="1"/>
-    <col min="3" max="3" width="20.3984375" customWidth="1"/>
-    <col min="4" max="4" width="28.73046875" customWidth="1"/>
-    <col min="5" max="5" width="31.1328125" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="29.25">
       <c r="A1" s="32" t="s">
         <v>36</v>
       </c>
@@ -1804,27 +2754,101 @@
       <c r="C1" s="32" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2">
-        <v>2017</v>
-      </c>
-      <c r="B2">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="C2">
-        <v>99.11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3">
-        <v>2022</v>
-      </c>
-      <c r="B3">
-        <v>68.45</v>
-      </c>
-      <c r="C3">
-        <v>171.12</v>
+      <c r="D1" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="32"/>
+      <c r="H1" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="35">
+        <v>2024</v>
+      </c>
+      <c r="B2" s="35">
+        <v>3.3738019169329001</v>
+      </c>
+      <c r="C2" s="35">
+        <v>0.56869009584663599</v>
+      </c>
+      <c r="D2" s="35">
+        <v>2.805111821086264</v>
+      </c>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="37">
+        <f>C2/B2</f>
+        <v>0.16856060606060363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="35">
+        <v>2030</v>
+      </c>
+      <c r="B3" s="35">
+        <v>4.3961661341853002</v>
+      </c>
+      <c r="C3" s="35">
+        <v>1.3546325878594221</v>
+      </c>
+      <c r="D3" s="35">
+        <v>3.0415335463258781</v>
+      </c>
+      <c r="E3" s="35">
+        <v>4.6389776357827399</v>
+      </c>
+      <c r="F3" s="35">
+        <v>5.3801916932907199</v>
+      </c>
+      <c r="G3" s="35"/>
+      <c r="H3" s="36">
+        <f>B3/B2</f>
+        <v>1.3030303030303048</v>
+      </c>
+      <c r="I3" s="37">
+        <f>C3/B3</f>
+        <v>0.30813953488372053</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="35">
+        <v>2040</v>
+      </c>
+      <c r="B4" s="35">
+        <v>5.6230031948881605</v>
+      </c>
+      <c r="C4" s="35">
+        <v>2.3706070287539798</v>
+      </c>
+      <c r="D4" s="35">
+        <v>3.2523961661341803</v>
+      </c>
+      <c r="E4" s="35">
+        <v>6.2428115015974202</v>
+      </c>
+      <c r="F4" s="35">
+        <v>7.0862619808306606</v>
+      </c>
+      <c r="G4" s="35"/>
+      <c r="H4" s="36">
+        <f>B4/B2</f>
+        <v>1.6666666666666647</v>
+      </c>
+      <c r="I4" s="37">
+        <f>C4/B4</f>
+        <v>0.42159090909090802</v>
       </c>
     </row>
   </sheetData>
@@ -1837,18 +2861,19 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.59765625" customWidth="1"/>
-    <col min="3" max="3" width="20.3984375" customWidth="1"/>
-    <col min="4" max="4" width="28.73046875" customWidth="1"/>
-    <col min="5" max="5" width="31.1328125" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="29.25">
       <c r="A1" s="32" t="s">
         <v>36</v>
       </c>
@@ -1858,27 +2883,101 @@
       <c r="C1" s="32" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2">
-        <v>2017</v>
-      </c>
-      <c r="B2">
-        <v>2.77</v>
-      </c>
-      <c r="C2">
-        <v>42.26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3">
-        <v>2022</v>
-      </c>
-      <c r="B3">
-        <v>9.61</v>
-      </c>
-      <c r="C3">
-        <v>96.51</v>
+      <c r="D1" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="32"/>
+      <c r="H1" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="35">
+        <v>2024</v>
+      </c>
+      <c r="B2" s="35">
+        <v>220.4472843450468</v>
+      </c>
+      <c r="C2" s="35">
+        <v>69.392971246006198</v>
+      </c>
+      <c r="D2" s="35">
+        <v>151.05431309904057</v>
+      </c>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="37">
+        <f>C2/B2</f>
+        <v>0.31478260869565289</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="35">
+        <v>2030</v>
+      </c>
+      <c r="B3" s="35">
+        <v>312.84345047923199</v>
+      </c>
+      <c r="C3" s="35">
+        <v>146.45367412140479</v>
+      </c>
+      <c r="D3" s="35">
+        <v>166.3897763578272</v>
+      </c>
+      <c r="E3" s="35">
+        <v>333.16293929712356</v>
+      </c>
+      <c r="F3" s="35">
+        <v>408.30670926517439</v>
+      </c>
+      <c r="G3" s="35"/>
+      <c r="H3" s="36">
+        <f>B3/B2</f>
+        <v>1.4191304347826104</v>
+      </c>
+      <c r="I3" s="37">
+        <f>C3/B3</f>
+        <v>0.46813725490195957</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="35">
+        <v>2040</v>
+      </c>
+      <c r="B4" s="35">
+        <v>328.17891373801922</v>
+      </c>
+      <c r="C4" s="35">
+        <v>133.4185303514364</v>
+      </c>
+      <c r="D4" s="35">
+        <v>194.76038338658282</v>
+      </c>
+      <c r="E4" s="35">
+        <v>374.18530351437602</v>
+      </c>
+      <c r="F4" s="35">
+        <v>437.44408945686837</v>
+      </c>
+      <c r="G4" s="35"/>
+      <c r="H4" s="36">
+        <f>B4/B2</f>
+        <v>1.488695652173921</v>
+      </c>
+      <c r="I4" s="37">
+        <f>C4/B4</f>
+        <v>0.40654205607476235</v>
       </c>
     </row>
   </sheetData>
@@ -1887,428 +2986,127 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11E3DE1-1E50-44AB-B589-DEB337CC2043}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1E8781-6A20-40D3-963A-0981D00A5D52}">
   <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
+    <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:9" ht="29.25">
+      <c r="A1" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="E1" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="F1" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="G1" s="32"/>
+      <c r="H1" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="I1" s="34" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="15">
-        <v>912</v>
-      </c>
-      <c r="D2" s="15">
-        <v>1095</v>
-      </c>
-      <c r="E2" s="15">
-        <f>AVERAGE(C2:D2)</f>
-        <v>1003.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="15">
-        <v>753</v>
-      </c>
-      <c r="D3" s="15">
-        <v>912</v>
-      </c>
-      <c r="E3" s="15">
-        <f t="shared" ref="E3:E23" si="0">AVERAGE(C3:D3)</f>
-        <v>832.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="15">
-        <v>850</v>
-      </c>
-      <c r="D4" s="15">
-        <v>1021</v>
-      </c>
-      <c r="E4" s="15">
-        <f t="shared" si="0"/>
-        <v>935.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="16">
-        <v>403</v>
-      </c>
-      <c r="D5" s="16">
-        <v>513</v>
-      </c>
-      <c r="E5" s="16">
-        <f t="shared" si="0"/>
-        <v>458</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="15">
-        <v>213</v>
-      </c>
-      <c r="D6" s="15">
-        <v>470</v>
-      </c>
-      <c r="E6" s="15">
-        <f t="shared" si="0"/>
-        <v>341.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="15">
-        <v>149</v>
-      </c>
-      <c r="D7" s="15">
-        <v>364</v>
-      </c>
-      <c r="E7" s="15">
-        <f t="shared" si="0"/>
-        <v>256.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="15">
-        <v>190</v>
-      </c>
-      <c r="D8" s="15">
-        <v>427</v>
-      </c>
-      <c r="E8" s="15">
-        <f t="shared" si="0"/>
-        <v>308.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="16">
-        <v>92</v>
-      </c>
-      <c r="D9" s="16">
-        <v>221</v>
-      </c>
-      <c r="E9" s="16">
-        <f t="shared" si="0"/>
-        <v>156.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="15">
-        <v>85</v>
-      </c>
-      <c r="D10" s="15">
-        <v>147</v>
-      </c>
-      <c r="E10" s="15">
-        <f t="shared" si="0"/>
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="15">
-        <v>6.1</v>
-      </c>
-      <c r="D11" s="15">
-        <v>11</v>
-      </c>
-      <c r="E11" s="15">
-        <f t="shared" si="0"/>
-        <v>8.5500000000000007</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="16">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="D12" s="16">
-        <v>6.4</v>
-      </c>
-      <c r="E12" s="16">
-        <f t="shared" si="0"/>
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A13" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="15">
-        <v>14</v>
-      </c>
-      <c r="D13" s="15">
-        <v>87</v>
-      </c>
-      <c r="E13" s="15">
-        <f t="shared" si="0"/>
-        <v>50.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A14" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="15">
-        <v>27</v>
-      </c>
-      <c r="D14" s="15">
-        <v>122</v>
-      </c>
-      <c r="E14" s="15">
-        <f t="shared" si="0"/>
-        <v>74.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A15" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="16">
-        <v>23</v>
-      </c>
-      <c r="D15" s="16">
-        <v>82</v>
-      </c>
-      <c r="E15" s="16">
-        <f t="shared" si="0"/>
-        <v>52.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A16" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="16">
-        <v>23</v>
-      </c>
-      <c r="D16" s="16">
-        <v>83</v>
-      </c>
-      <c r="E16" s="16">
-        <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A17" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="16">
-        <v>8</v>
-      </c>
-      <c r="D17" s="16">
-        <v>28</v>
-      </c>
-      <c r="E17" s="16">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A18" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" s="16">
-        <v>10</v>
-      </c>
-      <c r="D18" s="16">
-        <v>35</v>
-      </c>
-      <c r="E18" s="16">
-        <f t="shared" si="0"/>
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A19" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="16">
-        <v>7.4</v>
-      </c>
-      <c r="D19" s="16">
-        <v>27</v>
-      </c>
-      <c r="E19" s="16">
-        <f t="shared" si="0"/>
-        <v>17.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A20" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="16">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="D20" s="16">
-        <v>34</v>
-      </c>
-      <c r="E20" s="16">
-        <f t="shared" si="0"/>
-        <v>21.6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A21" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="15">
-        <v>7.8</v>
-      </c>
-      <c r="D21" s="15">
-        <v>16</v>
-      </c>
-      <c r="E21" s="15">
-        <f t="shared" si="0"/>
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A22" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="15">
-        <v>13</v>
-      </c>
-      <c r="D22" s="15">
-        <v>23</v>
-      </c>
-      <c r="E22" s="15">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A23" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" s="15">
-        <v>12</v>
-      </c>
-      <c r="D23" s="15">
-        <v>21</v>
-      </c>
-      <c r="E23" s="15">
-        <f t="shared" si="0"/>
-        <v>16.5</v>
+    <row r="2" spans="1:9">
+      <c r="A2" s="35">
+        <v>2024</v>
+      </c>
+      <c r="B2" s="35">
+        <v>4.4600638977635603</v>
+      </c>
+      <c r="C2" s="35">
+        <v>1.3162939297124521</v>
+      </c>
+      <c r="D2" s="35">
+        <v>3.143769968051108</v>
+      </c>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="37">
+        <f>C2/B2</f>
+        <v>0.29512893982807964</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="35">
+        <v>2030</v>
+      </c>
+      <c r="B3" s="35">
+        <v>7.4376996805111606</v>
+      </c>
+      <c r="C3" s="35">
+        <v>3.6038338658146922</v>
+      </c>
+      <c r="D3" s="35">
+        <v>3.8338658146964684</v>
+      </c>
+      <c r="E3" s="35">
+        <v>7.9999999999999609</v>
+      </c>
+      <c r="F3" s="35">
+        <v>10.108626198083041</v>
+      </c>
+      <c r="G3" s="35"/>
+      <c r="H3" s="36">
+        <f>B3/B2</f>
+        <v>1.6676217765043</v>
+      </c>
+      <c r="I3" s="37">
+        <f>C3/B3</f>
+        <v>0.48453608247422764</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="35">
+        <v>2040</v>
+      </c>
+      <c r="B4" s="35">
+        <v>9.738019169329041</v>
+      </c>
+      <c r="C4" s="35">
+        <v>4.7667731629392796</v>
+      </c>
+      <c r="D4" s="35">
+        <v>4.9712460063897606</v>
+      </c>
+      <c r="E4" s="35">
+        <v>11.591054313099001</v>
+      </c>
+      <c r="F4" s="35">
+        <v>14.134185303514361</v>
+      </c>
+      <c r="G4" s="35"/>
+      <c r="H4" s="36">
+        <f>B4/B2</f>
+        <v>2.1833810888252163</v>
+      </c>
+      <c r="I4" s="37">
+        <f>C4/B4</f>
+        <v>0.48950131233595784</v>
       </c>
     </row>
   </sheetData>
@@ -2317,318 +3115,127 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{154CC2AF-4989-4923-8B8E-B175B4ED0E63}">
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD4DAF6-E166-4500-8647-C984F8B27E6B}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19.1328125" customWidth="1"/>
-    <col min="2" max="2" width="23.1328125" customWidth="1"/>
-    <col min="3" max="3" width="15.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="15">
-        <v>66.297208538587796</v>
-      </c>
-      <c r="E2" s="15">
-        <v>53.160919540229202</v>
-      </c>
-      <c r="F2" s="15">
-        <v>13.067870826491003</v>
-      </c>
-      <c r="G2" s="6">
-        <v>0</v>
-      </c>
-      <c r="H2" s="15">
-        <v>39.340448823207993</v>
-      </c>
-      <c r="I2" s="6">
-        <v>0</v>
-      </c>
-      <c r="J2" s="15">
-        <v>24.904214559387015</v>
-      </c>
-      <c r="K2" s="15">
-        <v>9.0996168582379937</v>
-      </c>
-      <c r="L2" s="15">
-        <v>1.0946907498629912</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="6">
-        <v>0</v>
-      </c>
-      <c r="E3" s="15">
-        <v>22.304324028461899</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6">
-        <v>0</v>
-      </c>
-      <c r="J3" s="15">
-        <v>11.152162014231003</v>
-      </c>
-      <c r="K3" s="6">
-        <v>0</v>
-      </c>
-      <c r="L3" s="15">
-        <v>1.0946907498631973</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="16">
-        <v>7977.7920136664497</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="16">
-        <v>239.16292974590033</v>
-      </c>
-      <c r="I4" s="16">
-        <v>5473.4144778987511</v>
-      </c>
-      <c r="J4" s="16">
-        <v>778.98782831519929</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0</v>
-      </c>
-      <c r="L4" s="16">
-        <v>898.56929318810035</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="16">
-        <v>2897.2880632073402</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" s="16">
-        <v>416.82682041426051</v>
-      </c>
-      <c r="I5" s="16">
-        <v>5473.4144778987802</v>
-      </c>
-      <c r="J5" s="16">
-        <v>772.15460175101907</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0</v>
-      </c>
-      <c r="L5" s="16">
-        <v>591.07409780049966</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="16">
-        <v>2815.2893444373199</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="16">
-        <v>3860.7730087550699</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2">
-        <v>0</v>
-      </c>
-      <c r="L6" s="16">
-        <v>61.499039077520138</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="16">
-        <v>1141.1488362161001</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>720.90540251974971</v>
-      </c>
-      <c r="H7" s="2">
-        <v>307.49519538756999</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1093.31625026692</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2">
-        <v>47.832585949180157</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2">
-        <v>23.916292974579846</v>
+    <row r="1" spans="1:9" ht="29.25">
+      <c r="A1" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="32"/>
+      <c r="H1" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="35">
+        <v>2024</v>
+      </c>
+      <c r="B2" s="35">
+        <v>93.610223642172002</v>
+      </c>
+      <c r="C2" s="35">
+        <v>19.488817891373749</v>
+      </c>
+      <c r="D2" s="35">
+        <v>74.12140575079826</v>
+      </c>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="37">
+        <f>C2/B2</f>
+        <v>0.20819112627986408</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="35">
+        <v>2030</v>
+      </c>
+      <c r="B3" s="35">
+        <v>123.1629392971245</v>
+      </c>
+      <c r="C3" s="35">
+        <v>38.178913738019098</v>
+      </c>
+      <c r="D3" s="35">
+        <v>84.98402555910539</v>
+      </c>
+      <c r="E3" s="35">
+        <v>132.42811501597399</v>
+      </c>
+      <c r="F3" s="35">
+        <v>147.28434504792301</v>
+      </c>
+      <c r="G3" s="35"/>
+      <c r="H3" s="36">
+        <f>B3/B2</f>
+        <v>1.3156996587030778</v>
+      </c>
+      <c r="I3" s="37">
+        <f>C3/B3</f>
+        <v>0.30998702983138748</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="35">
+        <v>2040</v>
+      </c>
+      <c r="B4" s="35">
+        <v>149.68051118210849</v>
+      </c>
+      <c r="C4" s="35">
+        <v>46.805111821086044</v>
+      </c>
+      <c r="D4" s="35">
+        <v>102.87539936102246</v>
+      </c>
+      <c r="E4" s="35">
+        <v>163.57827476038298</v>
+      </c>
+      <c r="F4" s="35">
+        <v>172.68370607028749</v>
+      </c>
+      <c r="G4" s="35"/>
+      <c r="H4" s="36">
+        <f>B4/B2</f>
+        <v>1.5989761092150245</v>
+      </c>
+      <c r="I4" s="37">
+        <f>C4/B4</f>
+        <v>0.31270010672358473</v>
       </c>
     </row>
   </sheetData>
@@ -2898,39 +3505,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75B04653-368D-4396-B429-F735F1D4ABC0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75B04653-368D-4396-B429-F735F1D4ABC0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F87B3EE-5415-410A-AC93-A1F746B20A3D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
-    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F87B3EE-5415-410A-AC93-A1F746B20A3D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10B2F4FE-1C4B-46BF-9235-53580805D83F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
-    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10B2F4FE-1C4B-46BF-9235-53580805D83F}"/>
 </file>
--- a/02_Inputs/Data/Charts/Module 3 - Dasasets for Charts.xlsx
+++ b/02_Inputs/Data/Charts/Module 3 - Dasasets for Charts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/SEHCoreTeam/Shared Documents/General/04. Sustainable Energy Academy/SEA Charts and Infographics/SEA - Charts/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="769" documentId="11_86B3BED064903DA954D0E649743742B46DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89A3C398-822E-41AC-8077-6EB79B608FD7}"/>
+  <xr:revisionPtr revIDLastSave="775" documentId="11_86B3BED064903DA954D0E649743742B46DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B51F7C0E-B6F1-41F0-94B5-54E39D9DEF65}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2472,7 +2472,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9357577D-0713-4E4B-A3BB-AD68DAA30E7A}">
   <sheetPr>
-    <tabColor rgb="FF00B050"/>
+    <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -2601,7 +2601,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D96294-59C6-4D17-8187-7AF364170473}">
   <sheetPr>
-    <tabColor rgb="FF00B050"/>
+    <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -2730,7 +2730,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D97205A8-3FDC-47E2-8EDC-6BA2438A1FD9}">
   <sheetPr>
-    <tabColor rgb="FF00B050"/>
+    <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -2859,7 +2859,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D04D4904-CA5C-4DA0-9605-59863FBEE721}">
   <sheetPr>
-    <tabColor rgb="FF00B050"/>
+    <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -2988,7 +2988,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1E8781-6A20-40D3-963A-0981D00A5D52}">
   <sheetPr>
-    <tabColor rgb="FF00B050"/>
+    <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -3117,7 +3117,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD4DAF6-E166-4500-8647-C984F8B27E6B}">
   <sheetPr>
-    <tabColor rgb="FF00B050"/>
+    <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -3244,15 +3244,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010098970033F315F542A2D9640B7CC02236" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94449e8ff35cec47b43afd2e381d9e90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3" xmlns:ns3="c8670835-afc4-4376-8ae0-1ffed5b27e6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7f21ad7dc1dad656b5a5a7699096a32" ns2:_="" ns3:_="">
     <xsd:import namespace="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
@@ -3493,6 +3484,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3505,11 +3505,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75B04653-368D-4396-B429-F735F1D4ABC0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F87B3EE-5415-410A-AC93-A1F746B20A3D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F87B3EE-5415-410A-AC93-A1F746B20A3D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75B04653-368D-4396-B429-F735F1D4ABC0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
